--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/nov-2025.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/nov-2025.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>3134.54</v>
+        <v>3107.99</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1068.26</v>
+        <v>1059.21</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2266.94</v>
+        <v>2247.74</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>9948.43</v>
+        <v>9864.17</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>8347.34</v>
+        <v>8276.639999999999</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>4312.16</v>
+        <v>4290.01</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>774.97</v>
+        <v>770.98</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>9241.809999999999</v>
+        <v>9194.33</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>5314.76</v>
+        <v>5287.45</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1131.58</v>
+        <v>1125.76</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>32288.59</v>
+        <v>32122.69</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>767.5</v>
+        <v>763.55</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2840.98</v>
+        <v>2826.38</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1989.6</v>
+        <v>1979.37</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>858.54</v>
+        <v>854.13</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3747.87</v>
+        <v>3728.62</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>888.25</v>
+        <v>883.6799999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1379.43</v>
+        <v>1372.35</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>21350.47</v>
+        <v>21240.77</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>17633.83</v>
+        <v>17457.85</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>817.58</v>
+        <v>809.42</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>8174.37</v>
+        <v>8092.79</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2184.91</v>
+        <v>2163.11</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>5513.5</v>
+        <v>5458.47</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>17597.56</v>
+        <v>17421.94</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>987.23</v>
+        <v>977.38</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>902.05</v>
+        <v>893.04</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>17804.9</v>
+        <v>17627.2</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1572.11</v>
+        <v>1556.42</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>44011.17</v>
+        <v>43571.93</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>28708.49</v>
+        <v>28421.98</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1800.32</v>
+        <v>1782.35</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2747.04</v>
+        <v>2719.63</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>3980.22</v>
+        <v>3938.54</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>981.87</v>
+        <v>971.59</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1141.55</v>
+        <v>1129.59</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1238.85</v>
+        <v>1225.88</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2773.32</v>
+        <v>2744.27</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1048.23</v>
+        <v>1037.25</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>960.1900000000001</v>
+        <v>950.14</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1367.11</v>
+        <v>1352.79</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2201.66</v>
+        <v>2178.61</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>5585.55</v>
+        <v>5527.06</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1994.91</v>
+        <v>1974.02</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>7287.47</v>
+        <v>7211.15</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>24952.29</v>
+        <v>24690.99</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>2268.72</v>
+        <v>2244.96</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>821.59</v>
+        <v>817.09</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>6291.96</v>
+        <v>6257.57</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>17804</v>
+        <v>17706.69</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>7867.69</v>
+        <v>7824.68</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>9106.26</v>
+        <v>9056.49</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2985.96</v>
+        <v>2969.64</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>6974.43</v>
+        <v>6936.31</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>934.76</v>
+        <v>929.65</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>3304.48</v>
+        <v>3286.42</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>7329.43</v>
+        <v>7289.36</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>2816.82</v>
+        <v>2801.43</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>15084.06</v>
+        <v>15001.61</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>874.47</v>
+        <v>869.6900000000001</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>13134.31</v>
+        <v>13062.52</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>3039.86</v>
+        <v>3023.25</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>11442.53</v>
+        <v>11379.99</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>3740</v>
+        <v>3719.56</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>775.86</v>
+        <v>771.62</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>2041.2</v>
+        <v>2030.05</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>8433.52</v>
+        <v>8387.43</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1653.31</v>
+        <v>1644.28</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>28707.53</v>
+        <v>28387.69</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>10765.91</v>
+        <v>10645.96</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>9185.870000000001</v>
+        <v>9083.530000000001</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>7042.69</v>
+        <v>6964.23</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>5879.93</v>
+        <v>5814.42</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1486.06</v>
+        <v>1469.5</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>923.09</v>
+        <v>912.8099999999999</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>6247.93</v>
+        <v>6178.32</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1485.02</v>
+        <v>1476.89</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>5243.19</v>
+        <v>5214.47</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>810.26</v>
+        <v>805.83</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1045.82</v>
+        <v>1040.09</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>849</v>
+        <v>844.35</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>9295.99</v>
+        <v>9245.08</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>773.9</v>
+        <v>769.66</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>966.27</v>
+        <v>960.98</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2596.47</v>
+        <v>2582.25</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>947.47</v>
+        <v>942.28</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1355.21</v>
+        <v>1347.79</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>2726.02</v>
+        <v>2711.09</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>745.25</v>
+        <v>741.17</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>8094.3</v>
+        <v>8049.98</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>3660.43</v>
+        <v>3655.77</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>28027.2</v>
+        <v>27991.53</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1960.19</v>
+        <v>1957.7</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>952.75</v>
+        <v>951.54</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>4458.21</v>
+        <v>4452.53</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1762.4</v>
+        <v>1760.16</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>7723.56</v>
+        <v>7713.73</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>2089.61</v>
+        <v>2097.07</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>3577.21</v>
+        <v>3589.97</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>2795.95</v>
+        <v>2805.93</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1309.28</v>
+        <v>1313.95</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1678.4</v>
+        <v>1684.39</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>786.65</v>
+        <v>789.46</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>21666.96</v>
+        <v>21744.29</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1293.09</v>
+        <v>1297.71</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>3293.91</v>
+        <v>3305.66</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2211.1</v>
+        <v>2218.99</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1265.22</v>
+        <v>1269.73</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>3293.91</v>
+        <v>3305.66</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>20751.23</v>
+        <v>20825.29</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>3715.3</v>
+        <v>3728.56</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>64341.37</v>
+        <v>64571</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>962.71</v>
+        <v>973.1799999999999</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>2683.2</v>
+        <v>2712.38</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>1402.41</v>
+        <v>1417.66</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>11323.71</v>
+        <v>11446.87</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>9279.040000000001</v>
+        <v>9379.959999999999</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1444.74</v>
+        <v>1460.46</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>4620.15</v>
+        <v>4670.4</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>11150.08</v>
+        <v>11271.35</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>1208.62</v>
+        <v>1221.77</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>929.3200000000001</v>
+        <v>939.4299999999999</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>3261.54</v>
+        <v>3297.01</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>3494.08</v>
+        <v>3532.09</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>2112.6</v>
+        <v>2135.57</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1250.16</v>
+        <v>1263.76</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>2281.73</v>
+        <v>2306.55</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>5293.91</v>
+        <v>5351.49</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>5624.52</v>
+        <v>5685.7</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>3301.03</v>
+        <v>3336.93</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1402.56</v>
+        <v>1417.81</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>8229.370000000001</v>
+        <v>8318.879999999999</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>1121.58</v>
+        <v>1133.78</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>2096.81</v>
+        <v>2119.61</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>2925.31</v>
+        <v>2957.12</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>3223.2</v>
+        <v>3258.25</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1837.8</v>
+        <v>1857.78</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>8973.530000000001</v>
+        <v>9003.049999999999</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>14950.15</v>
+        <v>14999.32</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>2789.65</v>
+        <v>2798.82</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>750.25</v>
+        <v>752.72</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>1246.65</v>
+        <v>1250.75</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>6234.8</v>
+        <v>6255.31</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2669.72</v>
+        <v>2678.5</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>859.14</v>
+        <v>861.97</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>5348.71</v>
+        <v>5366.3</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>2803.14</v>
+        <v>2812.36</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>9488.719999999999</v>
+        <v>9519.93</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>3261.41</v>
+        <v>3272.14</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>1869</v>
+        <v>1875.15</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>3207.43</v>
+        <v>3217.97</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>5491.24</v>
+        <v>5509.3</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>6166.14</v>
+        <v>6186.42</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1348.71</v>
+        <v>1353.14</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>1155.92</v>
+        <v>1159.72</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2078.27</v>
+        <v>2085.11</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>754.48</v>
+        <v>756.96</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>4628.81</v>
+        <v>4644.04</v>
       </c>
     </row>
     <row r="160">
@@ -10203,7 +10203,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>1937.33</v>
+        <v>1943.71</v>
       </c>
     </row>
     <row r="161">
@@ -10264,7 +10264,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>837.3</v>
+        <v>840.05</v>
       </c>
     </row>
     <row r="162">
@@ -10325,7 +10325,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>15450.76</v>
+        <v>15717.46</v>
       </c>
     </row>
     <row r="163">
@@ -10386,7 +10386,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>1049.34</v>
+        <v>1067.45</v>
       </c>
     </row>
     <row r="164">
@@ -10447,7 +10447,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>2670.41</v>
+        <v>2716.51</v>
       </c>
     </row>
     <row r="165">
@@ -10508,7 +10508,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>16296.98</v>
+        <v>16578.29</v>
       </c>
     </row>
     <row r="166">
@@ -10569,7 +10569,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>1149.3</v>
+        <v>1169.14</v>
       </c>
     </row>
     <row r="167">
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>12942.13</v>
+        <v>13165.53</v>
       </c>
     </row>
     <row r="168">
@@ -10691,7 +10691,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>2734.64</v>
+        <v>2781.85</v>
       </c>
     </row>
     <row r="169">
@@ -10752,7 +10752,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>7838.36</v>
+        <v>7973.66</v>
       </c>
     </row>
     <row r="170">
@@ -10813,7 +10813,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>800.53</v>
+        <v>814.35</v>
       </c>
     </row>
     <row r="171">
@@ -10874,7 +10874,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>2779.09</v>
+        <v>2827.06</v>
       </c>
     </row>
     <row r="172">
@@ -10935,7 +10935,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1121.69</v>
+        <v>1141.06</v>
       </c>
     </row>
     <row r="173">
@@ -10996,7 +10996,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>4219.25</v>
+        <v>4292.08</v>
       </c>
     </row>
     <row r="174">
@@ -11057,7 +11057,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>769.65</v>
+        <v>782.9299999999999</v>
       </c>
     </row>
     <row r="175">
@@ -11118,7 +11118,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>1481.51</v>
+        <v>1507.08</v>
       </c>
     </row>
     <row r="176">
@@ -11179,7 +11179,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>1174.47</v>
+        <v>1194.74</v>
       </c>
     </row>
     <row r="177">
@@ -11240,7 +11240,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>27125</v>
+        <v>27593.22</v>
       </c>
     </row>
     <row r="178">
@@ -11301,7 +11301,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>25156.97</v>
+        <v>25591.22</v>
       </c>
     </row>
     <row r="179">
@@ -11362,7 +11362,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>2074.03</v>
+        <v>2109.83</v>
       </c>
     </row>
     <row r="180">
@@ -11423,7 +11423,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>5977.27</v>
+        <v>6080.44</v>
       </c>
     </row>
     <row r="181">
@@ -11484,7 +11484,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>12264.91</v>
+        <v>12476.62</v>
       </c>
     </row>
     <row r="182">
@@ -11545,7 +11545,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>5161.64</v>
+        <v>5250.74</v>
       </c>
     </row>
     <row r="183">
@@ -11606,7 +11606,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>9338.48</v>
+        <v>9499.68</v>
       </c>
     </row>
     <row r="184">
@@ -11667,7 +11667,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>7716.3</v>
+        <v>7849.5</v>
       </c>
     </row>
     <row r="185">
@@ -11728,7 +11728,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>10382.6</v>
+        <v>10561.82</v>
       </c>
     </row>
     <row r="186">
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>5385</v>
+        <v>5477.96</v>
       </c>
     </row>
     <row r="187">
@@ -11850,7 +11850,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>1086.76</v>
+        <v>1105.52</v>
       </c>
     </row>
     <row r="188">
@@ -11911,7 +11911,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>4749.86</v>
+        <v>4831.85</v>
       </c>
     </row>
     <row r="189">
@@ -11972,7 +11972,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>5435.24</v>
+        <v>5529.06</v>
       </c>
     </row>
     <row r="190">
@@ -12033,7 +12033,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>2935.27</v>
+        <v>2955.61</v>
       </c>
     </row>
     <row r="191">
@@ -12094,7 +12094,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>13615.56</v>
+        <v>13709.88</v>
       </c>
     </row>
     <row r="192">
@@ -12155,7 +12155,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>5374.22</v>
+        <v>5411.45</v>
       </c>
     </row>
     <row r="193">
@@ -12216,7 +12216,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>2089.11</v>
+        <v>2103.58</v>
       </c>
     </row>
     <row r="194">
@@ -12277,7 +12277,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>5838.02</v>
+        <v>5878.47</v>
       </c>
     </row>
     <row r="195">
@@ -12338,7 +12338,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>880.22</v>
+        <v>886.3200000000001</v>
       </c>
     </row>
     <row r="196">
@@ -12399,7 +12399,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>1281.91</v>
+        <v>1290.8</v>
       </c>
     </row>
     <row r="197">
@@ -12460,7 +12460,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>890.24</v>
+        <v>896.41</v>
       </c>
     </row>
     <row r="198">
@@ -12521,7 +12521,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>744.3</v>
+        <v>749.46</v>
       </c>
     </row>
     <row r="199">
@@ -12582,7 +12582,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>1669.53</v>
+        <v>1681.09</v>
       </c>
     </row>
     <row r="200">
@@ -12643,7 +12643,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>885.12</v>
+        <v>891.25</v>
       </c>
     </row>
     <row r="201">
@@ -12704,7 +12704,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>26717.51</v>
+        <v>26902.59</v>
       </c>
     </row>
     <row r="202">
@@ -12765,7 +12765,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>4420.12</v>
+        <v>4450.75</v>
       </c>
     </row>
     <row r="203">
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>13547.97</v>
+        <v>13641.82</v>
       </c>
     </row>
     <row r="204">
@@ -12887,7 +12887,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>762.9299999999999</v>
+        <v>768.21</v>
       </c>
     </row>
     <row r="205">
@@ -12948,7 +12948,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>11688.89</v>
+        <v>11769.87</v>
       </c>
     </row>
     <row r="206">
@@ -13009,7 +13009,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>7166.32</v>
+        <v>7215.97</v>
       </c>
     </row>
     <row r="207">
@@ -13070,7 +13070,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>872.95</v>
+        <v>879</v>
       </c>
     </row>
     <row r="208">
@@ -13131,7 +13131,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>2439.97</v>
+        <v>2451.34</v>
       </c>
     </row>
     <row r="209">
@@ -13192,7 +13192,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>945.74</v>
+        <v>950.14</v>
       </c>
     </row>
     <row r="210">
@@ -13253,7 +13253,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>893.45</v>
+        <v>897.61</v>
       </c>
     </row>
     <row r="211">
@@ -13314,7 +13314,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>901.48</v>
+        <v>905.6799999999999</v>
       </c>
     </row>
     <row r="212">
@@ -13375,7 +13375,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>950.78</v>
+        <v>955.21</v>
       </c>
     </row>
     <row r="213">
@@ -13436,7 +13436,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>1075.83</v>
+        <v>1080.84</v>
       </c>
     </row>
     <row r="214">
@@ -13497,7 +13497,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>3593.29</v>
+        <v>3610.02</v>
       </c>
     </row>
     <row r="215">
@@ -13558,7 +13558,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>6171.87</v>
+        <v>6200.61</v>
       </c>
     </row>
     <row r="216">
@@ -13619,7 +13619,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>1670.24</v>
+        <v>1678.02</v>
       </c>
     </row>
     <row r="217">
@@ -13680,7 +13680,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>821.1900000000001</v>
+        <v>825.02</v>
       </c>
     </row>
     <row r="218">
@@ -13741,7 +13741,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>884.6900000000001</v>
+        <v>888.8099999999999</v>
       </c>
     </row>
     <row r="219">
@@ -13802,7 +13802,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>1146.6</v>
+        <v>1151.94</v>
       </c>
     </row>
     <row r="220">
@@ -13863,7 +13863,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>9990.74</v>
+        <v>10037.26</v>
       </c>
     </row>
     <row r="221">
@@ -13924,7 +13924,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>5343.58</v>
+        <v>5368.47</v>
       </c>
     </row>
     <row r="222">
@@ -13985,7 +13985,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>2475.77</v>
+        <v>2487.3</v>
       </c>
     </row>
     <row r="223">
@@ -14046,7 +14046,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>68602.78999999999</v>
+        <v>68922.28</v>
       </c>
     </row>
     <row r="224">
@@ -14107,7 +14107,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>3293.5</v>
+        <v>3308.84</v>
       </c>
     </row>
     <row r="225">
@@ -14168,7 +14168,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>5290.6</v>
+        <v>5315.24</v>
       </c>
     </row>
     <row r="226">
@@ -14229,7 +14229,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>836.61</v>
+        <v>840.51</v>
       </c>
     </row>
     <row r="227">
@@ -14290,7 +14290,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>7000.91</v>
+        <v>7033.51</v>
       </c>
     </row>
     <row r="228">
@@ -14351,7 +14351,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>3631.33</v>
+        <v>3648.24</v>
       </c>
     </row>
     <row r="229">
@@ -14412,7 +14412,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>5004.75</v>
+        <v>5028.06</v>
       </c>
     </row>
     <row r="230">
@@ -14473,7 +14473,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>10681.54</v>
+        <v>10731.29</v>
       </c>
     </row>
     <row r="231">
@@ -14534,7 +14534,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>26993.34</v>
+        <v>27187.94</v>
       </c>
     </row>
     <row r="232">
@@ -14595,7 +14595,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>36500.68</v>
+        <v>36763.83</v>
       </c>
     </row>
     <row r="233">
@@ -14656,7 +14656,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>4158.98</v>
+        <v>4188.96</v>
       </c>
     </row>
     <row r="234">
@@ -14717,7 +14717,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>817.15</v>
+        <v>823.04</v>
       </c>
     </row>
     <row r="235">
@@ -14778,7 +14778,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>3375.62</v>
+        <v>3399.96</v>
       </c>
     </row>
     <row r="236">
@@ -14839,7 +14839,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>953.12</v>
+        <v>959.99</v>
       </c>
     </row>
     <row r="237">
@@ -14900,7 +14900,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>1290.12</v>
+        <v>1299.42</v>
       </c>
     </row>
     <row r="238">
@@ -14961,7 +14961,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>22349.92</v>
+        <v>22511.05</v>
       </c>
     </row>
     <row r="239">
@@ -15022,7 +15022,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>5677.08</v>
+        <v>5718.01</v>
       </c>
     </row>
     <row r="240">
@@ -15083,7 +15083,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>4008.65</v>
+        <v>4037.55</v>
       </c>
     </row>
     <row r="241">
@@ -15144,7 +15144,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>1182.42</v>
+        <v>1190.94</v>
       </c>
     </row>
     <row r="242">
@@ -15205,7 +15205,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>4184.72</v>
+        <v>4214.89</v>
       </c>
     </row>
     <row r="243">
@@ -15266,7 +15266,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>1271.27</v>
+        <v>1280.43</v>
       </c>
     </row>
     <row r="244">
@@ -15327,7 +15327,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>7480.71</v>
+        <v>7534.64</v>
       </c>
     </row>
     <row r="245">
@@ -15388,7 +15388,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>1031.6</v>
+        <v>1039.04</v>
       </c>
     </row>
     <row r="246">
@@ -15449,7 +15449,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>752.48</v>
+        <v>757.9</v>
       </c>
     </row>
     <row r="247">
@@ -15510,7 +15510,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>3256.16</v>
+        <v>3279.63</v>
       </c>
     </row>
     <row r="248">
@@ -15571,7 +15571,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>5461.87</v>
+        <v>5501.25</v>
       </c>
     </row>
     <row r="249">
@@ -15632,7 +15632,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>17746.51</v>
+        <v>17874.45</v>
       </c>
     </row>
     <row r="250">
@@ -15693,7 +15693,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>1193.06</v>
+        <v>1201.66</v>
       </c>
     </row>
     <row r="251">
@@ -15754,7 +15754,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>855.25</v>
+        <v>861.41</v>
       </c>
     </row>
     <row r="252">
@@ -15815,7 +15815,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>6162.48</v>
+        <v>6206.91</v>
       </c>
     </row>
     <row r="253">
@@ -15876,7 +15876,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>1042.73</v>
+        <v>1050.24</v>
       </c>
     </row>
     <row r="254">
@@ -15937,7 +15937,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>7831.87</v>
+        <v>7817.98</v>
       </c>
     </row>
     <row r="255">
@@ -15998,7 +15998,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>2353.72</v>
+        <v>2349.54</v>
       </c>
     </row>
     <row r="256">
@@ -16059,7 +16059,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>1797.56</v>
+        <v>1794.37</v>
       </c>
     </row>
     <row r="257">
@@ -16120,7 +16120,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>4945.69</v>
+        <v>4936.92</v>
       </c>
     </row>
     <row r="258">
@@ -16181,7 +16181,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>5124.95</v>
+        <v>5115.86</v>
       </c>
     </row>
     <row r="259">
@@ -16242,7 +16242,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>1294.67</v>
+        <v>1292.37</v>
       </c>
     </row>
     <row r="260">
@@ -16303,7 +16303,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>17581.45</v>
+        <v>17550.27</v>
       </c>
     </row>
     <row r="261">
@@ -16364,7 +16364,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>2932.09</v>
+        <v>2926.89</v>
       </c>
     </row>
     <row r="262">
@@ -16425,7 +16425,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>5267.5</v>
+        <v>5258.16</v>
       </c>
     </row>
     <row r="263">
@@ -16486,7 +16486,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>2861.5</v>
+        <v>2856.43</v>
       </c>
     </row>
     <row r="264">
@@ -16547,7 +16547,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>71777.14</v>
+        <v>71649.83</v>
       </c>
     </row>
     <row r="265">
@@ -16608,7 +16608,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>4632.91</v>
+        <v>4624.69</v>
       </c>
     </row>
     <row r="266">
@@ -16669,7 +16669,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>5569.63</v>
+        <v>5559.75</v>
       </c>
     </row>
     <row r="267">
@@ -16730,7 +16730,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>21296.9</v>
+        <v>21259.13</v>
       </c>
     </row>
     <row r="268">
@@ -16791,7 +16791,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>3107.19</v>
+        <v>3101.68</v>
       </c>
     </row>
     <row r="269">
@@ -16852,7 +16852,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>15160.84</v>
+        <v>15133.95</v>
       </c>
     </row>
     <row r="270">
@@ -16913,7 +16913,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>8081.52</v>
+        <v>8067.18</v>
       </c>
     </row>
     <row r="271">
@@ -16974,7 +16974,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>2970.71</v>
+        <v>2965.44</v>
       </c>
     </row>
     <row r="272">
@@ -17035,7 +17035,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>5975.39</v>
+        <v>5964.79</v>
       </c>
     </row>
     <row r="273">
@@ -17096,7 +17096,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>59056.82</v>
+        <v>58952.07</v>
       </c>
     </row>
     <row r="274">
@@ -17157,7 +17157,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>1453.41</v>
+        <v>1450.84</v>
       </c>
     </row>
     <row r="275">
@@ -17218,7 +17218,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>2391.9</v>
+        <v>2387.66</v>
       </c>
     </row>
     <row r="276">
@@ -17279,7 +17279,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>5182.53</v>
+        <v>5173.33</v>
       </c>
     </row>
     <row r="277">
@@ -17340,7 +17340,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>750.01</v>
+        <v>746.91</v>
       </c>
     </row>
     <row r="278">
@@ -17401,7 +17401,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>29117.37</v>
+        <v>28997.36</v>
       </c>
     </row>
     <row r="279">
@@ -17462,7 +17462,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>1872.45</v>
+        <v>1864.73</v>
       </c>
     </row>
     <row r="280">
@@ -17523,7 +17523,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>1323.62</v>
+        <v>1318.16</v>
       </c>
     </row>
     <row r="281">
@@ -17584,7 +17584,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>2417.26</v>
+        <v>2407.29</v>
       </c>
     </row>
     <row r="282">
@@ -17645,7 +17645,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>1917.84</v>
+        <v>1909.94</v>
       </c>
     </row>
     <row r="283">
@@ -17706,7 +17706,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>1946</v>
+        <v>1937.98</v>
       </c>
     </row>
     <row r="284">
@@ -17767,7 +17767,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>5710.29</v>
+        <v>5686.75</v>
       </c>
     </row>
     <row r="285">
@@ -17828,7 +17828,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>2151.68</v>
+        <v>2142.81</v>
       </c>
     </row>
     <row r="286">
@@ -17889,7 +17889,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>6009.85</v>
+        <v>5985.08</v>
       </c>
     </row>
     <row r="287">
@@ -17950,7 +17950,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>10782.28</v>
+        <v>10737.84</v>
       </c>
     </row>
     <row r="288">
@@ -18011,7 +18011,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>5968.91</v>
+        <v>5944.31</v>
       </c>
     </row>
     <row r="289">
@@ -18072,7 +18072,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>5177.87</v>
+        <v>5156.53</v>
       </c>
     </row>
     <row r="290">
@@ -18133,7 +18133,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>30920.85</v>
+        <v>30793.4</v>
       </c>
     </row>
     <row r="291">
@@ -18194,7 +18194,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>2188.25</v>
+        <v>2179.23</v>
       </c>
     </row>
     <row r="292">
@@ -18255,7 +18255,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>3959.63</v>
+        <v>3943.31</v>
       </c>
     </row>
     <row r="293">
@@ -18316,7 +18316,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>14836.46</v>
+        <v>14775.31</v>
       </c>
     </row>
     <row r="294">
@@ -18377,7 +18377,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>18716.82</v>
+        <v>18639.68</v>
       </c>
     </row>
     <row r="295">
@@ -18438,7 +18438,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>1028.11</v>
+        <v>1023.87</v>
       </c>
     </row>
     <row r="296">
@@ -18499,7 +18499,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>775.74</v>
+        <v>772.55</v>
       </c>
     </row>
     <row r="297">
@@ -18560,7 +18560,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>7030.8</v>
+        <v>7001.82</v>
       </c>
     </row>
     <row r="298">
@@ -18621,7 +18621,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>13769.32</v>
+        <v>13747.98</v>
       </c>
     </row>
     <row r="299">
@@ -18682,7 +18682,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>4007.71</v>
+        <v>4001.5</v>
       </c>
     </row>
     <row r="300">
@@ -18743,7 +18743,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>3877.97</v>
+        <v>3871.96</v>
       </c>
     </row>
     <row r="301">
@@ -18804,7 +18804,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>26868.23</v>
+        <v>26826.59</v>
       </c>
     </row>
     <row r="302">
@@ -18865,7 +18865,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>1044.43</v>
+        <v>1042.82</v>
       </c>
     </row>
     <row r="303">
@@ -18926,7 +18926,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>14528.8</v>
+        <v>14506.28</v>
       </c>
     </row>
     <row r="304">
@@ -18987,7 +18987,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>1698.22</v>
+        <v>1695.59</v>
       </c>
     </row>
     <row r="305">
@@ -19048,7 +19048,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>2747.04</v>
+        <v>2742.78</v>
       </c>
     </row>
     <row r="306">
@@ -19109,7 +19109,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>2967.18</v>
+        <v>2962.58</v>
       </c>
     </row>
     <row r="307">
@@ -19170,7 +19170,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>3950.09</v>
+        <v>3943.97</v>
       </c>
     </row>
     <row r="308">
@@ -19231,7 +19231,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>4591.77</v>
+        <v>4584.65</v>
       </c>
     </row>
     <row r="309">
@@ -19292,7 +19292,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>8637.92</v>
+        <v>8624.530000000001</v>
       </c>
     </row>
     <row r="310">
@@ -19353,7 +19353,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>3112.59</v>
+        <v>3107.76</v>
       </c>
     </row>
     <row r="311">
@@ -19414,7 +19414,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>4373.8</v>
+        <v>4367.02</v>
       </c>
     </row>
     <row r="312">
@@ -19475,7 +19475,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>2431.16</v>
+        <v>2427.4</v>
       </c>
     </row>
     <row r="313">
@@ -19536,7 +19536,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>15398.67</v>
+        <v>15374.8</v>
       </c>
     </row>
     <row r="314">
@@ -19597,7 +19597,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>23905.32</v>
+        <v>23868.27</v>
       </c>
     </row>
     <row r="315">
@@ -19658,7 +19658,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>9616.75</v>
+        <v>9601.84</v>
       </c>
     </row>
     <row r="316">
@@ -19719,7 +19719,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>3291.72</v>
+        <v>3286.61</v>
       </c>
     </row>
     <row r="317">
@@ -19780,7 +19780,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>3293.37</v>
+        <v>3288.26</v>
       </c>
     </row>
     <row r="318">
@@ -19841,7 +19841,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>14096.44</v>
+        <v>14074.59</v>
       </c>
     </row>
     <row r="319">
@@ -19902,7 +19902,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>2459.69</v>
+        <v>2455.88</v>
       </c>
     </row>
     <row r="320">
@@ -19963,7 +19963,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>5833.58</v>
+        <v>5824.54</v>
       </c>
     </row>
     <row r="321">
@@ -20024,7 +20024,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>1863.25</v>
+        <v>1860.36</v>
       </c>
     </row>
     <row r="322">
@@ -20085,7 +20085,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>13960.36</v>
+        <v>13938.72</v>
       </c>
     </row>
     <row r="323">
@@ -20146,7 +20146,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>29520.52</v>
+        <v>29474.77</v>
       </c>
     </row>
     <row r="324">
@@ -20207,7 +20207,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>1060.66</v>
+        <v>1059.02</v>
       </c>
     </row>
     <row r="325">
@@ -20268,7 +20268,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>20728.51</v>
+        <v>20696.38</v>
       </c>
     </row>
     <row r="326">
@@ -20329,7 +20329,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>2904.43</v>
+        <v>2899.93</v>
       </c>
     </row>
     <row r="327">
@@ -20390,7 +20390,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>66894.11</v>
+        <v>67239.58</v>
       </c>
     </row>
     <row r="328">
@@ -20451,7 +20451,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>8945.790000000001</v>
+        <v>8991.99</v>
       </c>
     </row>
     <row r="329">
@@ -20512,7 +20512,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>961</v>
+        <v>965.96</v>
       </c>
     </row>
     <row r="330">
@@ -20573,7 +20573,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>67167.33</v>
+        <v>67514.21000000001</v>
       </c>
     </row>
     <row r="331">
@@ -20634,7 +20634,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>829.35</v>
+        <v>833.64</v>
       </c>
     </row>
     <row r="332">
@@ -20695,7 +20695,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>1720.33</v>
+        <v>1729.21</v>
       </c>
     </row>
     <row r="333">
@@ -20756,7 +20756,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>7199.65</v>
+        <v>7236.83</v>
       </c>
     </row>
     <row r="334">
@@ -20817,7 +20817,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>7494.41</v>
+        <v>7533.11</v>
       </c>
     </row>
     <row r="335">
@@ -20878,7 +20878,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>4000.38</v>
+        <v>4021.04</v>
       </c>
     </row>
     <row r="336">
@@ -20939,7 +20939,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>1792.19</v>
+        <v>1801.45</v>
       </c>
     </row>
     <row r="337">
@@ -21000,7 +21000,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>784.11</v>
+        <v>788.16</v>
       </c>
     </row>
     <row r="338">
@@ -21061,7 +21061,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>29977.64</v>
+        <v>30132.45</v>
       </c>
     </row>
     <row r="339">
@@ -21122,7 +21122,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>5367.93</v>
+        <v>5395.66</v>
       </c>
     </row>
     <row r="340">
@@ -21183,7 +21183,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>1624.19</v>
+        <v>1632.58</v>
       </c>
     </row>
     <row r="341">
@@ -21244,7 +21244,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>8442.940000000001</v>
+        <v>8486.540000000001</v>
       </c>
     </row>
     <row r="342">
@@ -21305,7 +21305,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>822.47</v>
+        <v>826.71</v>
       </c>
     </row>
     <row r="343">
@@ -21366,7 +21366,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>2835.19</v>
+        <v>2849.84</v>
       </c>
     </row>
     <row r="344">
@@ -21427,7 +21427,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>4807.44</v>
+        <v>4832.27</v>
       </c>
     </row>
     <row r="345">
@@ -21488,7 +21488,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>2587.53</v>
+        <v>2600.89</v>
       </c>
     </row>
     <row r="346">
@@ -21549,7 +21549,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>8624.780000000001</v>
+        <v>8669.33</v>
       </c>
     </row>
     <row r="347">
@@ -21610,7 +21610,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>1183.65</v>
+        <v>1189.76</v>
       </c>
     </row>
     <row r="348">
@@ -21671,7 +21671,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>7431.46</v>
+        <v>7469.84</v>
       </c>
     </row>
     <row r="349">
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>3140.01</v>
+        <v>3162.17</v>
       </c>
     </row>
     <row r="350">
@@ -21793,7 +21793,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>15213.69</v>
+        <v>15321.06</v>
       </c>
     </row>
     <row r="351">
@@ -21854,7 +21854,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>3258.83</v>
+        <v>3281.83</v>
       </c>
     </row>
     <row r="352">
@@ -21915,7 +21915,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>5604.13</v>
+        <v>5643.68</v>
       </c>
     </row>
     <row r="353">
@@ -21976,7 +21976,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>2572.27</v>
+        <v>2590.42</v>
       </c>
     </row>
     <row r="354">
@@ -22037,7 +22037,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>3549.87</v>
+        <v>3574.93</v>
       </c>
     </row>
     <row r="355">
@@ -22098,7 +22098,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>2299.22</v>
+        <v>2315.45</v>
       </c>
     </row>
     <row r="356">
@@ -22159,7 +22159,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>2997.09</v>
+        <v>3018.24</v>
       </c>
     </row>
     <row r="357">
@@ -22220,7 +22220,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>5909.1</v>
+        <v>5950.8</v>
       </c>
     </row>
     <row r="358">
@@ -22281,7 +22281,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>3088.38</v>
+        <v>3110.18</v>
       </c>
     </row>
     <row r="359">
@@ -22342,7 +22342,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>782.85</v>
+        <v>788.37</v>
       </c>
     </row>
     <row r="360">
@@ -22403,7 +22403,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>833.9</v>
+        <v>839.78</v>
       </c>
     </row>
     <row r="361">
@@ -22464,7 +22464,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>6868.8</v>
+        <v>6917.27</v>
       </c>
     </row>
     <row r="362">
@@ -22525,7 +22525,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>1526.55</v>
+        <v>1537.33</v>
       </c>
     </row>
     <row r="363">
@@ -22586,7 +22586,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>7590.23</v>
+        <v>7643.8</v>
       </c>
     </row>
     <row r="364">
@@ -22647,7 +22647,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>973.64</v>
+        <v>980.51</v>
       </c>
     </row>
     <row r="365">
@@ -22708,7 +22708,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>6880.51</v>
+        <v>6929.07</v>
       </c>
     </row>
     <row r="366">
@@ -22769,7 +22769,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>19855.58</v>
+        <v>19995.71</v>
       </c>
     </row>
     <row r="367">
@@ -22830,7 +22830,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>1412.86</v>
+        <v>1422.83</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/nov-2025.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/nov-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC nov-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC nov-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10549,7 +10549,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -13050,7 +13050,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14026,7 +14026,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14087,7 +14087,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14392,7 +14392,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14453,7 +14453,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14636,7 +14636,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -15551,7 +15551,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15612,7 +15612,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -16039,7 +16039,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16588,7 +16588,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16893,7 +16893,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -18601,7 +18601,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -19394,7 +19394,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19577,7 +19577,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19699,7 +19699,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -19821,7 +19821,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -19943,7 +19943,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -20797,7 +20797,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -20919,7 +20919,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -21407,7 +21407,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -22688,7 +22688,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/nov-2025.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/nov-2025.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FISCALIZACION Y CONTROL</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>FISCALIZACION Y CONTROL</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Colina 1</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>BUQUE ESCUELA ESMERALDA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Academia Politécnica Naval</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>CENTRO DE EDUCACION INTEGRAL DE ADULTOS FERMIN FIERRO LUENGO</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VIII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Museo Marítimo Nacional</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cementerio General</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>BASE INFANTERIA DE MARINA CONCON</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Academia Politécnica Naval</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dirección de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dirección de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (V)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Academia Politécnica Naval</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>ESCUELA DE GRUMETES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Colina 1</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>ENERGÍA DEL FUTURO</t>
+          <t>Energía del Futuro</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>PROGRAMA DE VIALIDAD Y TRANSPORTE URBANO SECTRA</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA ORLANDO ANTONIO</t>
+          <t>Comercializadora orlando antonio</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA ORLANDO ANTONIO</t>
+          <t>Comercializadora orlando antonio</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>FONDO PARA HOSPITALES DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>FONDO PARA HOSPITALES DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>FONDO PARA HOSPITALES DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10180,7 +10180,11 @@
           <t>61.980.840-1</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
       <c r="H160" t="inlineStr">
         <is>
           <t>Aysén</t>
@@ -10300,7 +10304,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Santa Rosa</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA ROSA</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10422,7 +10426,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - X Zona Los Lagos</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10666,7 +10670,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10732,7 +10736,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10910,7 +10914,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Servicio Electoral</t>
+          <t>SERVICIO ELECTORAL</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11154,7 +11158,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11764,7 +11768,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11825,7 +11829,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -12008,7 +12012,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12140,7 +12144,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA PROINMIN SPA</t>
+          <t>Importadora y Comercializadora Proinmin SpA</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -12252,7 +12256,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>ESCUELA NAVAL "ARTURO PRAT"</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12374,7 +12378,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Hospital de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12628,7 +12632,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Quality Rubber S.A.</t>
+          <t>QUALITY RUBBER S.A.</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -12679,7 +12683,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>FISCALIZACION Y CONTROL</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12801,7 +12805,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12862,7 +12866,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -13045,7 +13049,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13238,7 +13242,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -13350,7 +13354,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13416,7 +13420,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13838,7 +13842,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - VIII Zona Bio Bio</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13960,7 +13964,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - VIII Zona Bio Bio</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14326,12 +14330,12 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14448,7 +14452,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14509,7 +14513,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Universidad de Chile - Bienestar del Personal</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -14824,7 +14828,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -15119,7 +15123,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>ESCUELA NAVAL "ARTURO PRAT"</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15424,7 +15428,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15546,7 +15550,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15607,7 +15611,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -15790,7 +15794,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>ADMINISTRACIÓN ADUANA DE CHAÑARAL</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -16034,7 +16038,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16161,7 +16165,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16522,12 +16526,12 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16832,7 +16836,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16888,7 +16892,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17010,7 +17014,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17254,7 +17258,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Punilla Cordil</t>
+          <t>Servicio Local de Educación Pública Punilla Cordillera</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -17508,7 +17512,7 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;AMP; EXPORTADORA UNINNOV EIRL</t>
+          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;amp; EXPORTADORA UNINNOV EIRL</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
@@ -17569,7 +17573,7 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;AMP; EXPORTADORA UNINNOV EIRL</t>
+          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;amp; EXPORTADORA UNINNOV EIRL</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
@@ -17803,7 +17807,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA METROPOLITANA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -17864,7 +17868,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -17874,7 +17878,7 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>FRANCISCO JAVIER</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
@@ -17925,12 +17929,12 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -18596,7 +18600,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN CO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -18840,7 +18844,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -18901,7 +18905,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -19267,7 +19271,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE ANTOFAGASTA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -19328,7 +19332,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -19389,7 +19393,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN CO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -19755,7 +19759,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -19816,7 +19820,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - VIII Zona Bio Bio</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -19877,7 +19881,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>SERVICIO HIDROGRAFICO Y OCEANOGRAFICO DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -19999,7 +20003,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -20060,12 +20064,12 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20121,12 +20125,12 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -20182,7 +20186,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -20243,12 +20247,12 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -20304,7 +20308,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -20365,7 +20369,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -20426,7 +20430,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GORBEA</t>
+          <t>Municipalidad de Gorbea</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -20731,7 +20735,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -20914,7 +20918,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Dirección de Educación Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -21158,7 +21162,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -21463,7 +21467,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -21473,7 +21477,7 @@
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;AMP; EXPORTADORA UNINNOV EIRL</t>
+          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;amp; EXPORTADORA UNINNOV EIRL</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
@@ -21585,7 +21589,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Servicio Agricola y Ganadero</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -21829,7 +21833,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -22073,7 +22077,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -22571,7 +22575,7 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
@@ -22693,7 +22697,7 @@
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>ENERGÍA DEL FUTURO</t>
+          <t>Energía del Futuro</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
@@ -22744,7 +22748,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -22805,7 +22809,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/nov-2025.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/nov-2025.xlsx
@@ -562,7 +562,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +871,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +936,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1062,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1127,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1253,11 @@
           <t>77.512.806-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1379,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1566,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1631,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1757,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2005,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2070,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2196,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2261,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3058,11 @@
           <t>76.317.833-1</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3184,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3371,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3497,11 @@
           <t>76.193.188-1</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3562,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3688,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3814,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4245,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4432,11 @@
           <t>52.003.040-9</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4497,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4684,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +4932,11 @@
           <t>76.317.833-1</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5058,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5123,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5249,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5558,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5745,11 @@
           <t>77.787.617-1</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6054,11 @@
           <t>76.698.741-9</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6119,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6367,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6676,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6741,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +6867,11 @@
           <t>77.787.617-1</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7115,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7302,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7489,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7676,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7741,11 @@
           <t>77.787.617-1</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +7806,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +7932,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +7997,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8611,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8676,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +8863,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +8989,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9115,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9180,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9428,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9493,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9558,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +9867,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +9993,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10241,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10428,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10554,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +10802,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +10928,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +10993,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11058,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11245,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11310,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11558,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11684,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +11871,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +11936,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12001,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12127,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12253,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12379,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12505,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +12814,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13184,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13432,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13497,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +13867,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +13993,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14058,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14428,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +14493,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +14558,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +14623,11 @@
           <t>77.743.864-6</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +14688,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +14814,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +14879,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15005,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15070,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15318,11 @@
           <t>77.575.038-3</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15383,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +15509,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +15940,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16005,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16314,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +16440,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +16505,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16570,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +16696,11 @@
           <t>84.634.200-1</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17005,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17131,11 @@
           <t>77.303.388-9</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17196,11 @@
           <t>76.712.337-K</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17261,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17326,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +17452,11 @@
           <t>77.787.617-1</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +17761,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +17887,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18257,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +18688,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +18753,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +18879,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19066,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19131,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +19440,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +19505,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +19814,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +19879,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +20066,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20131,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20196,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19899,7 +20383,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +20448,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +20513,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20265,7 +20761,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +21009,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +21257,11 @@
           <t>77.724.409-4</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +21322,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20875,7 +21387,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20936,7 +21452,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +21578,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +21704,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21241,7 +21769,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22078,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21668,7 +22204,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +22635,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22217,7 +22761,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22400,7 +22948,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22461,7 +23013,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22522,7 +23078,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22644,7 +23204,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22827,7 +23391,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/nov-2025.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/nov-2025.xlsx
@@ -5810,7 +5810,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13562,7 +13566,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15196,7 +15204,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23143,7 +23155,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
